--- a/historial/historial_facturas_usuario_2026-06-26.xlsx
+++ b/historial/historial_facturas_usuario_2026-06-26.xlsx
@@ -461,27 +461,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R55"/>
+  <dimension ref="A1:R104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="9" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4184,24 +4184,3860 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>Extracción facturas | Fecha: 2026-06-26 | Hora: 13:20:45 | Nº facturas: 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>BaseImp</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>BaseIRPF</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>FEscaneo</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>FFactura</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>FOperacion</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>ImporIVA</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>Moneda</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>NombreProveedor</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>NumeroFactura</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>PedidoCliente</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA2</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA3</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>TotalFact</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>_7HZ0JGKBW.pdf</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>4.301,380</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>B-91349282</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>MIGASAACEITES,S.L.U.</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:20:28</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>903,290</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>SINFIBANDA.NET</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>L/781</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>PCMI26-22538</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>B-91950253</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>21,00</t>
+        </is>
+      </c>
+      <c r="P58" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q58" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>5.204,670</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>16876.pdf</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>14.664,48</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>FR04341192227</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>ITMALIMENTAIREINTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:20:31</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Compañía Extremeña de Aceites y Cereales SL (CEXAC, S.L.)</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>X26214791</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>04593983 (1)</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>B10002475</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q59" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>14.664,48</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>26344.003014.pdf</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:20:32</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O60" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P60" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q60" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R60" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>844899755_74024075.pdf</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>-314,19</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>A91399774</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>OLEOSALGADOS.A.</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:20:34</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>12-MAR-2025</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>12-MAR-2025</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>-65,98</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>RICOH España S.L.U.</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>844899755</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>PCS2500063</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>ESB82080177</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P61" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q61" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>-380,17</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>844913777_74056244.pdf</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>1.340,23</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>B91616227</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>GRUPOYBARRAALIMENTACIONSL</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:20:35</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>08-ABR-2025</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>08-ABR-2025</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>281,45</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>RICOH España S.L.U.</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>844913777</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>PCAY25-00106</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>ESB82080177</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>21,00</t>
+        </is>
+      </c>
+      <c r="P62" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q62" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>1.621,68</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>845194771_74079214.pdf</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>32,50</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>B01958040</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>ACEITESSIMONROSASL</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:20:37</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>06-FEB-2026</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>06-FEB-2026</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>6,83</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>RICOH España S.L.U.</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>845194771</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>PC01-01006</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>ESB82080177</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>21,00</t>
+        </is>
+      </c>
+      <c r="P63" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q63" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>39,33</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>845302798_74096538.pdf</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>7,27</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>B90041633</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>MIGASAENVASADOSLU</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:20:39</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>06-JUN-2026</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>06-JUN-2026</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>1,53</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>RICOH España S.L.U.</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>845302798</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>PCEN26-00128</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>ESB82080177</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P64" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q64" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>8,80</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>2607053843.pdf</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>17210,27</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>A91399774</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>OLEOSALGADO,S.A.</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:20:40</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>3614,16</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>MOSCA MARÍTIMO S.L.</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>2607053843</t>
+        </is>
+      </c>
+      <c r="M65" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>B30464721</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P65" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q65" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>20824,43</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>261511107418.pdf</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>1.972,26</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>ES B91616227</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>GRUPOYBARRAALIMENTACION,S.L.</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:20:42</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>414,17</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>Smurft Westrock, S.A.</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>261511107418</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>PCAY26-13322</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>A-21.044.649</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>21,00</t>
+        </is>
+      </c>
+      <c r="P66" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q66" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R66" s="3" t="inlineStr">
+        <is>
+          <t>2.386,43</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>COMP. EXT. DE ACEITES Y CEREALES SL FPSEE12026002275.pdf</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>1506,00</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>ESB10002475</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>COMP.EXT.DEACEITESYCEREALESSL</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:20:43</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>ETE LOGISTICA ESPAÑA, SOC LIMITADA</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>FPSEE12026/002275</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>SOI-EE1__26/00002316</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>ESB13790779</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q67" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R67" s="3" t="inlineStr">
+        <is>
+          <t>1506,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>COMP. EXT. DE ACEITES Y CEREALES SL FPSEE12026002276.pdf</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>1346,00</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>ESB10002475</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>COMP.EXT.DEACEITESYCEREALESSL</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:20:45</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>ETE LOGISTICA ESPAÑA, SOC LIMITADA</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>FPSEE12026/002276</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>XPEXP260400</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>ESB13790779</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q68" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R68" s="3" t="inlineStr">
+        <is>
+          <t>1346,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>Extracción facturas | Fecha: 2026-06-26 | Hora: 13:22:24 | Nº facturas: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>BaseImp</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>BaseIRPF</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>FEscaneo</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>FFactura</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>FOperacion</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>ImporIVA</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Moneda</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>NombreProveedor</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>NumeroFactura</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>PedidoCliente</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA2</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA3</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>TotalFact</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>_7HZ0JGKBW.pdf</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>4.301,380</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>B-91349282</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>MIGASAACEITES,S.L.U.</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:22:22</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>903,290</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>SINFIBANDA.NET</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>L/781</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>PCMI26-22538</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>B-91950253</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>21,00</t>
+        </is>
+      </c>
+      <c r="P71" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q71" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R71" s="3" t="inlineStr">
+        <is>
+          <t>5.204,670</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>16876.pdf</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>14.664,48</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>FR04341192227</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>ITMALIMENTAIREINTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:22:24</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>Compañía Extremeña de Aceites y Cereales SL (CEXAC, S.L.)</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>X26214791</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>04593983 (1)</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
+          <t>B10002475</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q72" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R72" s="3" t="inlineStr">
+        <is>
+          <t>14.664,48</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>Extracción facturas | Fecha: 2026-06-26 | Hora: 13:22:49 | Nº facturas: 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>BaseImp</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>BaseIRPF</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>FEscaneo</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>FFactura</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>FOperacion</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>ImporIVA</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Moneda</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>NombreProveedor</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>NumeroFactura</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>PedidoCliente</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA2</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA3</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>TotalFact</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Report50398.pdf</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>1009904,4</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>B91950253</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>MIGASAACEITES,S.L.U.</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:22:39</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>100990,44</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>MENGIBAR, S.A.</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>2606-002136</t>
+        </is>
+      </c>
+      <c r="M75" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
+          <t>A41174970</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P75" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q75" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R75" s="3" t="inlineStr">
+        <is>
+          <t>1.110.894,84</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Report50507_split_1.pdf</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>26.502,96</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>B10002475</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>CEXACSL</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:22:40</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>23/06/26</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>23/06/26</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>1.060,12</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>ACEITES 1881 S.L.</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>26-000670</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>XPC26-11069</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
+          <t>B90450842</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P76" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q76" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R76" s="3" t="inlineStr">
+        <is>
+          <t>27.563,08</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Report50507_split_2.pdf</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>14.596,56</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>B10002475</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>CEXACSL</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:22:42</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>12/06/26</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>12/06/26</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>583,86</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>ACEITES 1881 S.L.</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>26-000643</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>XPC26-09873</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
+          <t>B90450842</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P77" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q77" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R77" s="3" t="inlineStr">
+        <is>
+          <t>15.180,42</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>SKM_C45826062517100.pdf</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>9.241,97</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>B55463905</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>MIGASASPECIALTYOILSSOCIEDADLIMITADA</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:22:45</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>1.940,81</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>ACEITES NATURALES DEL SUR S.L.</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>1/000003</t>
+        </is>
+      </c>
+      <c r="M78" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>B23651664</t>
+        </is>
+      </c>
+      <c r="O78" s="3" t="inlineStr">
+        <is>
+          <t>21,00</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>10,00</t>
+        </is>
+      </c>
+      <c r="Q78" s="3" t="inlineStr">
+        <is>
+          <t>4,00</t>
+        </is>
+      </c>
+      <c r="R78" s="3" t="inlineStr">
+        <is>
+          <t>13.928,78</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>T9015537326-051326.pdf</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>136.50</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>A41012766</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>MIGUELGALLEGOS.A.</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:22:46</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>5/13/26</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>5/13/26</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>28.67</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>Mango Technologies Inc Dba ClickUp</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>ES2026-8319</t>
+        </is>
+      </c>
+      <c r="M79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
+          <t>EU372085827</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+      <c r="P79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R79" s="3" t="inlineStr">
+        <is>
+          <t>165.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>T9015537326-060826.pdf</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>126.25</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>A41012766</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>MIGUELGALLEGOS.A.</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:22:49</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>6/8/26</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>6/8/26</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>26.51</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>Mango Technologies, Inc. DBA ClickUp</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>ES2026-9836</t>
+        </is>
+      </c>
+      <c r="M80" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
+          <t>EU372085827</t>
+        </is>
+      </c>
+      <c r="O80" s="3" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+      <c r="P80" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q80" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R80" s="3" t="inlineStr">
+        <is>
+          <t>152.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>Extracción facturas | Fecha: 2026-06-26 | Hora: 13:32:17 | Nº facturas: 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>BaseImp</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>BaseIRPF</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>FEscaneo</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>FFactura</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>FOperacion</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>ImporIVA</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Moneda</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>NombreProveedor</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>NumeroFactura</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>PedidoCliente</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA2</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA3</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>TotalFact</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>_7HZ0JGKBW.pdf</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>4.301,380</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>B-91349282</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>MIGASAACEITES,S.L.U.</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:32:10</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>903,290</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>SINFIBANDA.NET</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>L/781</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>PCMI26-22538</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
+          <t>B-91950253</t>
+        </is>
+      </c>
+      <c r="O83" s="3" t="inlineStr">
+        <is>
+          <t>21,00</t>
+        </is>
+      </c>
+      <c r="P83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R83" s="3" t="inlineStr">
+        <is>
+          <t>5.204,670</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>16876.pdf</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>14.664,48</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>FR04341192227</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>ITMALIMENTAIREINTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:32:12</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>Compañía Extremeña de Aceites y Cereales SL (CEXAC, S.L.)</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>X26214791</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>04593983 (1)</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
+          <t>B10002475</t>
+        </is>
+      </c>
+      <c r="O84" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P84" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q84" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R84" s="3" t="inlineStr">
+        <is>
+          <t>14.664,48</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>26344.003014.pdf</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:32:13</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>844899755_74024075.pdf</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>-314,19</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>A91399774</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>OLEOSALGADOS.A.</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:32:14</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>12-MAR-2025</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>12-MAR-2025</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>-65,98</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>RICOH España S.L.U.</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>844899755</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>PCS2500063</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
+          <t>ESB82080177</t>
+        </is>
+      </c>
+      <c r="O86" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P86" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q86" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R86" s="3" t="inlineStr">
+        <is>
+          <t>-380,17</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>844913777_74056244.pdf</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>1.340,23</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>B91616227</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>GRUPOYBARRAALIMENTACIONSL</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:32:16</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>08-ABR-2025</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>08-ABR-2025</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>281,45</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>RICOH España S.L.U.</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>844913777</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>PCAY25-00106</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
+          <t>ESB82080177</t>
+        </is>
+      </c>
+      <c r="O87" s="3" t="inlineStr">
+        <is>
+          <t>21,00</t>
+        </is>
+      </c>
+      <c r="P87" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q87" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R87" s="3" t="inlineStr">
+        <is>
+          <t>1.621,68</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>845194771_74079214.pdf</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>32,50</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>B01958040</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>ACEITESSIMONROSASL</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:32:17</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>06-FEB-2026</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>06-FEB-2026</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>6,83</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>RICOH España S.L.U.</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>845194771</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>PC01-01006</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
+          <t>ESB82080177</t>
+        </is>
+      </c>
+      <c r="O88" s="3" t="inlineStr">
+        <is>
+          <t>21,00</t>
+        </is>
+      </c>
+      <c r="P88" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q88" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R88" s="3" t="inlineStr">
+        <is>
+          <t>39,33</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>Extracción facturas | Fecha: 2026-06-26 | Hora: 13:34:46 | Nº facturas: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>BaseImp</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>BaseIRPF</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>FEscaneo</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>FFactura</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>FOperacion</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>ImporIVA</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>Moneda</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>NombreProveedor</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>NumeroFactura</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>PedidoCliente</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA2</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA3</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>TotalFact</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>_7HZ0JGKBW.pdf</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>4.301,380</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>B-91349282</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>MIGASAACEITES,S.L.U.</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:34:44</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>903,290</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>SINFIBANDA.NET</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>L/781</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>PCMI26-22538</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
+          <t>B-91950253</t>
+        </is>
+      </c>
+      <c r="O91" s="3" t="inlineStr">
+        <is>
+          <t>21,00</t>
+        </is>
+      </c>
+      <c r="P91" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q91" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R91" s="3" t="inlineStr">
+        <is>
+          <t>5.204,670</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>16876.pdf</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>14.664,48</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>FR04341192227</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>ITMALIMENTAIREINTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:34:46</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>Compañía Extremeña de Aceites y Cereales SL (CEXAC, S.L.)</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>X26214791</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>04593983 (1)</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
+          <t>B10002475</t>
+        </is>
+      </c>
+      <c r="O92" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P92" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q92" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R92" s="3" t="inlineStr">
+        <is>
+          <t>14.664,48</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>Extracción facturas | Fecha: 2026-06-26 | Hora: 13:36:18 | Nº facturas: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>BaseImp</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>BaseIRPF</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>FEscaneo</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>FFactura</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>FOperacion</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>ImporIVA</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>Moneda</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>NombreProveedor</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>NumeroFactura</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>PedidoCliente</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA2</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA3</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>TotalFact</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>_7HZ0JGKBW.pdf</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>4.301,380</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>B-91349282</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>MIGASAACEITES,S.L.U.</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:36:16</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>903,290</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>SINFIBANDA.NET</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>L/781</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>PCMI26-22538</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
+          <t>B-91950253</t>
+        </is>
+      </c>
+      <c r="O95" s="3" t="inlineStr">
+        <is>
+          <t>21,00</t>
+        </is>
+      </c>
+      <c r="P95" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q95" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R95" s="3" t="inlineStr">
+        <is>
+          <t>5.204,670</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>16876.pdf</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>14.664,48</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>FR04341192227</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>ITMALIMENTAIREINTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:36:18</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>Compañía Extremeña de Aceites y Cereales SL (CEXAC, S.L.)</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>X26214791</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>04593983 (1)</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
+          <t>B10002475</t>
+        </is>
+      </c>
+      <c r="O96" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P96" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q96" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R96" s="3" t="inlineStr">
+        <is>
+          <t>14.664,48</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>Extracción facturas | Fecha: 2026-06-26 | Hora: 13:37:12 | Nº facturas: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>BaseImp</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>BaseIRPF</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>FEscaneo</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>FFactura</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>FOperacion</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>ImporIVA</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>Moneda</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>NombreProveedor</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>NumeroFactura</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>PedidoCliente</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA2</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA3</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>TotalFact</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>_7HZ0JGKBW.pdf</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>4.301,380</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>B-91349282</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>MIGASAACEITES,S.L.U.</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:37:10</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>903,290</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>SINFIBANDA.NET</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>L/781</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>PCMI26-22538</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
+          <t>B-91950253</t>
+        </is>
+      </c>
+      <c r="O99" s="3" t="inlineStr">
+        <is>
+          <t>21,00</t>
+        </is>
+      </c>
+      <c r="P99" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q99" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R99" s="3" t="inlineStr">
+        <is>
+          <t>5.204,670</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>16876.pdf</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>14.664,48</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>FR04341192227</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>ITMALIMENTAIREINTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:37:12</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>Compañía Extremeña de Aceites y Cereales SL (CEXAC, S.L.)</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>X26214791</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>04593983 (1)</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
+          <t>B10002475</t>
+        </is>
+      </c>
+      <c r="O100" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P100" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q100" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R100" s="3" t="inlineStr">
+        <is>
+          <t>14.664,48</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>Extracción facturas | Fecha: 2026-06-26 | Hora: 13:49:28 | Nº facturas: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>BaseImp</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>BaseIRPF</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>FEscaneo</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>FFactura</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>FOperacion</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>ImporIVA</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Moneda</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>NombreProveedor</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>NumeroFactura</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>PedidoCliente</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA2</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>TipoIVA3</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>TotalFact</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>_7HZ0JGKBW.pdf</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>4.301,380</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>B-91349282</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>MIGASAACEITES,S.L.U.</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:49:25</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>903,290</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>SINFIBANDA.NET</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>L/781</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>PCMI26-22538</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
+          <t>B-91950253</t>
+        </is>
+      </c>
+      <c r="O103" s="3" t="inlineStr">
+        <is>
+          <t>21,00</t>
+        </is>
+      </c>
+      <c r="P103" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q103" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R103" s="3" t="inlineStr">
+        <is>
+          <t>5.204,670</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>16876.pdf</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>14.664,48</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>FR04341192227</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>ITMALIMENTAIREINTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>26/06/2026 13:49:28</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>Compañía Extremeña de Aceites y Cereales SL (CEXAC, S.L.)</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>X26214791</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>04593983 (1)</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
+          <t>B10002475</t>
+        </is>
+      </c>
+      <c r="O104" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P104" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q104" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R104" s="3" t="inlineStr">
+        <is>
+          <t>14.664,48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A53:R53"/>
+  <mergeCells count="24">
+    <mergeCell ref="A69:R69"/>
     <mergeCell ref="A7:R7"/>
     <mergeCell ref="A25:R25"/>
     <mergeCell ref="A41:R41"/>
     <mergeCell ref="A16:R16"/>
+    <mergeCell ref="A89:R89"/>
+    <mergeCell ref="A56:R56"/>
+    <mergeCell ref="A101:R101"/>
+    <mergeCell ref="A97:R97"/>
+    <mergeCell ref="A22:R22"/>
+    <mergeCell ref="A4:R4"/>
+    <mergeCell ref="A53:R53"/>
+    <mergeCell ref="A81:R81"/>
     <mergeCell ref="A19:R19"/>
-    <mergeCell ref="A49:R49"/>
     <mergeCell ref="A10:R10"/>
     <mergeCell ref="A28:R28"/>
+    <mergeCell ref="A93:R93"/>
     <mergeCell ref="A13:R13"/>
+    <mergeCell ref="A31:R31"/>
+    <mergeCell ref="A34:R34"/>
+    <mergeCell ref="A73:R73"/>
+    <mergeCell ref="A49:R49"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A45:R45"/>
-    <mergeCell ref="A31:R31"/>
-    <mergeCell ref="A22:R22"/>
-    <mergeCell ref="A34:R34"/>
-    <mergeCell ref="A4:R4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
